--- a/019-085-WENDLANDT-VENTAS/src/WendlandtVentas.Web/wwwroot/resources/Cotizacion.xlsx
+++ b/019-085-WENDLANDT-VENTAS/src/WendlandtVentas.Web/wwwroot/resources/Cotizacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WENDLANDT SYS\Wend-Sys\019-085-WENDLANDT-VENTAS\src\WendlandtVentas.Web\wwwroot\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8493A0-C8B9-4B55-9148-A31F9B2C6990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40996FD-EDAE-40F1-B3C1-5C15014E7B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F49A7E6-679B-4399-A417-11073B80C7DF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F49A7E6-679B-4399-A417-11073B80C7DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>CANT</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>COTIZACIÓN</t>
+  </si>
+  <si>
+    <t>*Pedido sujeto a disponibilidad de inventario al momento de su preparación.</t>
   </si>
 </sst>
 </file>
@@ -342,7 +345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -398,6 +401,57 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -407,80 +461,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -497,46 +536,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -940,14 +940,14 @@
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="7"/>
@@ -963,14 +963,14 @@
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="38">
+      <c r="E3" s="53">
         <v>5932</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="7"/>
@@ -986,14 +986,14 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="56"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -1009,41 +1009,41 @@
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35" t="s">
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35" t="s">
+      <c r="H5" s="26"/>
+      <c r="I5" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="35"/>
+      <c r="J5" s="26"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
     </row>
     <row r="6" spans="1:20" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="60"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="29"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
@@ -1059,12 +1059,12 @@
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="6"/>
@@ -1080,14 +1080,14 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="61" t="s">
+      <c r="E8" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
@@ -1103,12 +1103,12 @@
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="64"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="33"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -1124,12 +1124,12 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="67"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="36"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -1145,42 +1145,42 @@
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="37"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
     </row>
     <row r="13" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
@@ -1208,359 +1208,359 @@
       <c r="B14" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="54" t="s">
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H14" s="55"/>
-      <c r="I14" s="51" t="s">
+      <c r="H14" s="67"/>
+      <c r="I14" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="53"/>
+      <c r="J14" s="65"/>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
-      <c r="Q14" s="56"/>
-      <c r="R14" s="56"/>
-      <c r="S14" s="57"/>
-      <c r="T14" s="57"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
     </row>
     <row r="15" spans="1:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="47"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="46"/>
       <c r="L15" s="13"/>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="49"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
     </row>
     <row r="16" spans="1:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="47"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
       <c r="L16" s="13"/>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="49"/>
-      <c r="T16" s="49"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
     </row>
     <row r="17" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="47"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
       <c r="L17" s="13"/>
       <c r="M17" s="17"/>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
     </row>
     <row r="18" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B18" s="3"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="47"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="46"/>
       <c r="L18" s="13"/>
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
       <c r="O18" s="17"/>
       <c r="P18" s="17"/>
-      <c r="Q18" s="48"/>
-      <c r="R18" s="48"/>
-      <c r="S18" s="49"/>
-      <c r="T18" s="49"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="39"/>
     </row>
     <row r="19" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B19" s="3"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="47"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="46"/>
       <c r="L19" s="13"/>
       <c r="M19" s="17"/>
       <c r="N19" s="17"/>
       <c r="O19" s="17"/>
       <c r="P19" s="17"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="39"/>
     </row>
     <row r="20" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="47"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
       <c r="L20" s="13"/>
       <c r="M20" s="17"/>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="48"/>
-      <c r="S20" s="49"/>
-      <c r="T20" s="49"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="39"/>
     </row>
     <row r="21" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B21" s="3"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="47"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="46"/>
       <c r="L21" s="13"/>
       <c r="M21" s="17"/>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
       <c r="P21" s="17"/>
-      <c r="Q21" s="48"/>
-      <c r="R21" s="48"/>
-      <c r="S21" s="49"/>
-      <c r="T21" s="49"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="39"/>
     </row>
     <row r="22" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="47"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
       <c r="L22" s="13"/>
       <c r="M22" s="17"/>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
-      <c r="Q22" s="48"/>
-      <c r="R22" s="48"/>
-      <c r="S22" s="49"/>
-      <c r="T22" s="49"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="39"/>
+      <c r="T22" s="39"/>
     </row>
     <row r="23" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="47"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
       <c r="K23" s="9"/>
       <c r="L23" s="13"/>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
       <c r="O23" s="17"/>
       <c r="P23" s="17"/>
-      <c r="Q23" s="48"/>
-      <c r="R23" s="48"/>
-      <c r="S23" s="49"/>
-      <c r="T23" s="49"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="39"/>
     </row>
     <row r="24" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="47"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="46"/>
       <c r="L24" s="13"/>
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
       <c r="O24" s="17"/>
       <c r="P24" s="17"/>
-      <c r="Q24" s="48"/>
-      <c r="R24" s="48"/>
-      <c r="S24" s="49"/>
-      <c r="T24" s="49"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="39"/>
     </row>
     <row r="25" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B25" s="21"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="47"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
       <c r="L25" s="13"/>
       <c r="M25" s="17"/>
       <c r="N25" s="17"/>
       <c r="O25" s="17"/>
       <c r="P25" s="17"/>
-      <c r="Q25" s="48"/>
-      <c r="R25" s="48"/>
-      <c r="S25" s="49"/>
-      <c r="T25" s="49"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="39"/>
+      <c r="T25" s="39"/>
     </row>
     <row r="26" spans="2:20" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="47"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
       <c r="N26" s="19"/>
       <c r="O26" s="19"/>
       <c r="P26" s="19"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
     </row>
     <row r="27" spans="2:20" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="47"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
       <c r="L27" s="18"/>
       <c r="M27" s="18"/>
       <c r="N27" s="19"/>
       <c r="O27" s="19"/>
       <c r="P27" s="19"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="49"/>
-      <c r="T27" s="49"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="39"/>
+      <c r="T27" s="39"/>
     </row>
     <row r="28" spans="2:20" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="30"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="60"/>
       <c r="L28" s="18"/>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="18"/>
       <c r="P28" s="18"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="32"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
     </row>
     <row r="29" spans="2:20" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="30"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="60"/>
       <c r="L29" s="18"/>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
       <c r="O29" s="18"/>
       <c r="P29" s="18"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="32"/>
-      <c r="T29" s="32"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
     </row>
     <row r="30" spans="2:20" s="4" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="33" t="s">
+      <c r="C30" s="40"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
       <c r="N30" s="20"/>
       <c r="O30" s="20"/>
       <c r="P30" s="20"/>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="36"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="37"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
     </row>
     <row r="31" spans="2:20" s="4" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="25"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="42"/>
       <c r="L31" s="18"/>
       <c r="M31" s="18"/>
       <c r="N31" s="20"/>
@@ -1568,40 +1568,44 @@
       <c r="P31" s="20"/>
     </row>
     <row r="32" spans="2:20" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
       <c r="G32" s="68"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
       <c r="L32" s="12"/>
       <c r="M32" s="12"/>
       <c r="N32" s="10"/>
       <c r="O32" s="10"/>
       <c r="P32" s="10"/>
     </row>
-    <row r="33" spans="2:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="22"/>
+    <row r="33" spans="2:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="22" t="s">
+        <v>13</v>
+      </c>
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
       <c r="L33" s="8"/>
       <c r="P33" s="8"/>
     </row>
     <row r="34" spans="2:19" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
       <c r="G34" s="8"/>
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
@@ -1652,72 +1656,30 @@
     <row r="64" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="112">
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E9:J10"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="S24:T24"/>
+  <mergeCells count="113">
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
     <mergeCell ref="Q29:R29"/>
     <mergeCell ref="S29:T29"/>
     <mergeCell ref="G30:H30"/>
@@ -1742,29 +1704,72 @@
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E9:J10"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="C15:F15"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="69" orientation="landscape" r:id="rId1"/>
